--- a/charts/piechart.xlsx
+++ b/charts/piechart.xlsx
@@ -8,13 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jcsaez/proyectos/lin-reveal/charts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668CDFD5-5BFF-D64A-AE95-2540D42F1E75}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A453877-5ECD-4440-BBA9-F6F017C05EC2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7240" yWindow="440" windowWidth="28040" windowHeight="16640" xr2:uid="{7C48BCD4-E921-6742-BB0D-97EB786F495C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$2:$A$6</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$B$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$B$2:$B$6</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$A$2:$A$6</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$B$1</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$2:$B$6</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$A$2:$A$6</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$B$1</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$B$2:$B$6</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -553,6 +564,13 @@
                 </c:ext>
               </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
@@ -626,19 +644,19 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.41420000000000001</c:v>
+                  <c:v>0.44440000000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.30859999999999999</c:v>
+                  <c:v>0.27479999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.161</c:v>
+                  <c:v>0.18190000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.6500000000000004E-2</c:v>
+                  <c:v>5.5599999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.5799999999999998E-2</c:v>
+                  <c:v>4.1099999999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1621,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.41420000000000001</v>
+        <v>0.44440000000000002</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1629,7 +1647,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0.30859999999999999</v>
+        <v>0.27479999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1637,7 +1655,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>0.161</v>
+        <v>0.18190000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1645,7 +1663,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>6.6500000000000004E-2</v>
+        <v>5.5599999999999997E-2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1653,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>3.5799999999999998E-2</v>
+        <v>4.1099999999999998E-2</v>
       </c>
     </row>
   </sheetData>

--- a/charts/piechart.xlsx
+++ b/charts/piechart.xlsx
@@ -8,24 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jcsaez/proyectos/lin-reveal/charts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A453877-5ECD-4440-BBA9-F6F017C05EC2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D717F468-F506-8A47-8BCA-18F28BEC390C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7240" yWindow="440" windowWidth="28040" windowHeight="16640" xr2:uid="{7C48BCD4-E921-6742-BB0D-97EB786F495C}"/>
+    <workbookView xWindow="7240" yWindow="460" windowWidth="28040" windowHeight="16640" xr2:uid="{7C48BCD4-E921-6742-BB0D-97EB786F495C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$2:$A$6</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$B$1</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$B$2:$B$6</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$A$2:$A$6</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$B$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$B$2:$B$6</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$A$2:$A$6</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$B$1</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet1!$B$2:$B$6</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -115,7 +104,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -378,7 +367,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-ES"/>
+                  <a:endParaRPr lang="es-ES"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="outEnd"/>
@@ -417,7 +406,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-ES"/>
+                  <a:endParaRPr lang="es-ES"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="outEnd"/>
@@ -456,7 +445,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-ES"/>
+                  <a:endParaRPr lang="es-ES"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="outEnd"/>
@@ -495,7 +484,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-ES"/>
+                  <a:endParaRPr lang="es-ES"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="outEnd"/>
@@ -540,7 +529,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-ES"/>
+                  <a:endParaRPr lang="es-ES"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -585,7 +574,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-ES"/>
+                <a:endParaRPr lang="es-ES"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -644,19 +633,19 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0.44440000000000002</c:v>
+                  <c:v>0.45379999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.27479999999999999</c:v>
+                  <c:v>0.25609999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.18190000000000001</c:v>
+                  <c:v>0.18390000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.5599999999999997E-2</c:v>
+                  <c:v>5.5300000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.1099999999999998E-2</c:v>
+                  <c:v>4.1500000000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -714,7 +703,7 @@
       <a:pPr>
         <a:defRPr sz="1200"/>
       </a:pPr>
-      <a:endParaRPr lang="en-ES"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1327,7 +1316,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1639,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.44440000000000002</v>
+        <v>0.45379999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1647,7 +1636,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0.27479999999999999</v>
+        <v>0.25609999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1655,7 +1644,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>0.18190000000000001</v>
+        <v>0.18390000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1663,7 +1652,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>5.5599999999999997E-2</v>
+        <v>5.5300000000000002E-2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1671,7 +1660,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>4.1099999999999998E-2</v>
+        <v>4.1500000000000002E-2</v>
       </c>
     </row>
   </sheetData>
